--- a/fixtures/xlsx/column-widths/input.xlsx
+++ b/fixtures/xlsx/column-widths/input.xlsx
@@ -16,9 +16,6 @@
     <t>Normal</t>
   </si>
   <si>
-    <t>a longer piece of text</t>
-  </si>
-  <si>
     <t>medium text</t>
   </si>
   <si>
@@ -26,6 +23,9 @@
   </si>
   <si>
     <t>short</t>
+  </si>
+  <si>
+    <t>a longer piece of text</t>
   </si>
 </sst>
 </file>
@@ -39,7 +39,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -50,13 +50,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/xlsx/column-widths/input.xlsx
+++ b/fixtures/xlsx/column-widths/input.xlsx
@@ -10,16 +10,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Wide</t>
+    <t>medium text</t>
   </si>
   <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>medium text</t>
+    <t>Narrow</t>
   </si>
   <si>
-    <t>Narrow</t>
+    <t>Wide</t>
   </si>
   <si>
     <t>short</t>
@@ -39,10 +39,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -56,7 +56,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
